--- a/vrcc.xlsx
+++ b/vrcc.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/davidackuaku/Desktop/VRCC/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1904C0E6-C999-6844-873B-D5E4D385BDA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{809BF978-595E-6B44-8889-23D4AFA8F882}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="33600" windowHeight="21000" activeTab="1" xr2:uid="{690D29BB-E107-B54C-8AFA-AAD6A1551766}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" activeTab="1" xr2:uid="{690D29BB-E107-B54C-8AFA-AAD6A1551766}"/>
   </bookViews>
   <sheets>
     <sheet name="projects" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">media!$A$1:$E$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">media!$A$1:$E$28</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="103">
   <si>
     <t>District</t>
   </si>
@@ -344,6 +344,12 @@
   </si>
   <si>
     <t>https://res.cloudinary.com/dgclahox/image/upload/v1790439237/HM_EM01.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dgclahox/video/upload/v1791793577/HM_EM006.mp4</t>
+  </si>
+  <si>
+    <t>The ongoing 24 Hour Economy Market at Ho Titrinu</t>
   </si>
 </sst>
 </file>
@@ -1095,8 +1101,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{751A449C-0CEB-BA49-A044-736BF91FB682}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="2" max="2" width="89.5" customWidth="1"/>
@@ -1120,7 +1125,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="2" spans="1:5" hidden="1">
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
         <v>29</v>
       </c>
@@ -1137,7 +1142,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:5" hidden="1">
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
         <v>29</v>
       </c>
@@ -1154,7 +1159,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:5" hidden="1">
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
         <v>29</v>
       </c>
@@ -1239,7 +1244,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:5" hidden="1">
+    <row r="9" spans="1:5">
       <c r="A9" t="s">
         <v>58</v>
       </c>
@@ -1256,7 +1261,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:5" hidden="1">
+    <row r="10" spans="1:5">
       <c r="A10" t="s">
         <v>58</v>
       </c>
@@ -1273,7 +1278,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:5" hidden="1">
+    <row r="11" spans="1:5">
       <c r="A11" t="s">
         <v>58</v>
       </c>
@@ -1290,7 +1295,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:5" hidden="1">
+    <row r="12" spans="1:5">
       <c r="A12" t="s">
         <v>58</v>
       </c>
@@ -1307,7 +1312,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:5" hidden="1">
+    <row r="13" spans="1:5">
       <c r="A13" t="s">
         <v>34</v>
       </c>
@@ -1324,7 +1329,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:5" hidden="1">
+    <row r="14" spans="1:5">
       <c r="A14" t="s">
         <v>34</v>
       </c>
@@ -1341,7 +1346,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:5" hidden="1">
+    <row r="15" spans="1:5">
       <c r="A15" t="s">
         <v>34</v>
       </c>
@@ -1358,7 +1363,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:5" hidden="1">
+    <row r="16" spans="1:5">
       <c r="A16" t="s">
         <v>34</v>
       </c>
@@ -1375,7 +1380,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:5" hidden="1">
+    <row r="17" spans="1:5">
       <c r="A17" t="s">
         <v>29</v>
       </c>
@@ -1392,7 +1397,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:5" hidden="1">
+    <row r="18" spans="1:5">
       <c r="A18" t="s">
         <v>29</v>
       </c>
@@ -1409,7 +1414,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="51" hidden="1">
+    <row r="19" spans="1:5" ht="51">
       <c r="A19" t="s">
         <v>29</v>
       </c>
@@ -1474,7 +1479,7 @@
         <v>87</v>
       </c>
       <c r="E22">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1491,10 +1496,10 @@
         <v>87</v>
       </c>
       <c r="E23">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" hidden="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
       <c r="A24" t="s">
         <v>80</v>
       </c>
@@ -1511,7 +1516,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:5" hidden="1">
+    <row r="25" spans="1:5">
       <c r="A25" t="s">
         <v>80</v>
       </c>
@@ -1528,7 +1533,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:5" hidden="1">
+    <row r="26" spans="1:5">
       <c r="A26" t="s">
         <v>80</v>
       </c>
@@ -1555,18 +1560,32 @@
       <c r="C27" t="s">
         <v>55</v>
       </c>
+      <c r="D27" t="s">
+        <v>87</v>
+      </c>
       <c r="E27">
         <v>2</v>
       </c>
     </row>
+    <row r="28" spans="1:5">
+      <c r="A28" t="s">
+        <v>33</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="C28" t="s">
+        <v>102</v>
+      </c>
+      <c r="D28" t="s">
+        <v>64</v>
+      </c>
+      <c r="E28">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E26" xr:uid="{751A449C-0CEB-BA49-A044-736BF91FB682}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="HM002"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:E28" xr:uid="{751A449C-0CEB-BA49-A044-736BF91FB682}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E16">
     <sortCondition ref="A1:A16"/>
   </sortState>
@@ -1598,6 +1617,7 @@
     <hyperlink ref="B25" r:id="rId24" xr:uid="{2D947D41-7D25-5C4E-A45B-9C6F931BF54F}"/>
     <hyperlink ref="B26" r:id="rId25" xr:uid="{BD0EF741-44F5-B849-8574-53C9AD78F4AD}"/>
     <hyperlink ref="B27" r:id="rId26" xr:uid="{97819A27-9770-AC4D-AB83-857D3AB7B217}"/>
+    <hyperlink ref="B28" r:id="rId27" xr:uid="{DDA6D94F-261D-3544-84CA-DD279F702337}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/vrcc.xlsx
+++ b/vrcc.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/davidackuaku/Desktop/VRCC/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{809BF978-595E-6B44-8889-23D4AFA8F882}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1A01CAD-1758-8747-A086-C574891F1108}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" activeTab="1" xr2:uid="{690D29BB-E107-B54C-8AFA-AAD6A1551766}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="33600" windowHeight="21000" activeTab="1" xr2:uid="{690D29BB-E107-B54C-8AFA-AAD6A1551766}"/>
   </bookViews>
   <sheets>
     <sheet name="projects" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">media!$A$1:$E$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">media!$A$1:$E$29</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="105">
   <si>
     <t>District</t>
   </si>
@@ -289,9 +289,6 @@
     <t>Ho Dave</t>
   </si>
   <si>
-    <t xml:space="preserve">Construction of Astro Turf </t>
-  </si>
-  <si>
     <t>The construction of Astro Turf at Ho School of Hygyiene.</t>
   </si>
   <si>
@@ -301,9 +298,6 @@
     <t>Site picture.</t>
   </si>
   <si>
-    <t xml:space="preserve">Work going on at the site. </t>
-  </si>
-  <si>
     <t>image</t>
   </si>
   <si>
@@ -350,6 +344,18 @@
   </si>
   <si>
     <t>The ongoing 24 Hour Economy Market at Ho Titrinu</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dgclahox/video/upload/v1791794403/HM_AT005.mp4</t>
+  </si>
+  <si>
+    <t>Video of the ongoing Astroturf at the School of Hygiene, Ho.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Construction of Astro turf </t>
+  </si>
+  <si>
+    <t>First site meeting for the construction Starting for the 24 Hr Economy Market</t>
   </si>
 </sst>
 </file>
@@ -1073,7 +1079,7 @@
         <v>3</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="D9">
         <v>6.5918999999999999</v>
@@ -1082,7 +1088,7 @@
         <v>0.51739999999999997</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G9" t="s">
         <v>4</v>
@@ -1101,7 +1107,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{751A449C-0CEB-BA49-A044-736BF91FB682}">
-  <dimension ref="A1:E28"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="2" max="2" width="89.5" customWidth="1"/>
@@ -1125,7 +1132,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" hidden="1">
       <c r="A2" t="s">
         <v>29</v>
       </c>
@@ -1136,13 +1143,13 @@
         <v>54</v>
       </c>
       <c r="D2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" hidden="1">
       <c r="A3" t="s">
         <v>29</v>
       </c>
@@ -1153,13 +1160,13 @@
         <v>54</v>
       </c>
       <c r="D3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E3">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" hidden="1">
       <c r="A4" t="s">
         <v>29</v>
       </c>
@@ -1170,7 +1177,7 @@
         <v>54</v>
       </c>
       <c r="D4" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -1187,7 +1194,7 @@
         <v>55</v>
       </c>
       <c r="D5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E5">
         <v>3</v>
@@ -1204,7 +1211,7 @@
         <v>56</v>
       </c>
       <c r="D6" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E6">
         <v>4</v>
@@ -1218,10 +1225,10 @@
         <v>44</v>
       </c>
       <c r="C7" t="s">
-        <v>56</v>
+        <v>104</v>
       </c>
       <c r="D7" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E7">
         <v>5</v>
@@ -1235,16 +1242,16 @@
         <v>45</v>
       </c>
       <c r="C8" t="s">
-        <v>56</v>
+        <v>104</v>
       </c>
       <c r="D8" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E8">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" hidden="1">
       <c r="A9" t="s">
         <v>58</v>
       </c>
@@ -1255,13 +1262,13 @@
         <v>57</v>
       </c>
       <c r="D9" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E9">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" hidden="1">
       <c r="A10" t="s">
         <v>58</v>
       </c>
@@ -1272,13 +1279,13 @@
         <v>57</v>
       </c>
       <c r="D10" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E10">
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" hidden="1">
       <c r="A11" t="s">
         <v>58</v>
       </c>
@@ -1289,13 +1296,13 @@
         <v>57</v>
       </c>
       <c r="D11" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E11">
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" hidden="1">
       <c r="A12" t="s">
         <v>58</v>
       </c>
@@ -1306,81 +1313,81 @@
         <v>57</v>
       </c>
       <c r="D12" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E12">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" hidden="1">
       <c r="A13" t="s">
         <v>34</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C13" t="s">
         <v>71</v>
       </c>
       <c r="D13" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E13">
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" hidden="1">
       <c r="A14" t="s">
         <v>34</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C14" t="s">
         <v>71</v>
       </c>
       <c r="D14" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E14">
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" hidden="1">
       <c r="A15" t="s">
         <v>34</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C15" t="s">
         <v>71</v>
       </c>
       <c r="D15" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E15">
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" hidden="1">
       <c r="A16" t="s">
         <v>34</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C16" t="s">
         <v>71</v>
       </c>
       <c r="D16" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E16">
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" hidden="1">
       <c r="A17" t="s">
         <v>29</v>
       </c>
@@ -1397,7 +1404,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" hidden="1">
       <c r="A18" t="s">
         <v>29</v>
       </c>
@@ -1414,7 +1421,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="51">
+    <row r="19" spans="1:5" ht="51" hidden="1">
       <c r="A19" t="s">
         <v>29</v>
       </c>
@@ -1439,10 +1446,10 @@
         <v>44</v>
       </c>
       <c r="C20" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="D20" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E20">
         <v>7</v>
@@ -1453,13 +1460,13 @@
         <v>33</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C21" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D21" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E21">
         <v>1</v>
@@ -1470,13 +1477,13 @@
         <v>33</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C22" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D22" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E22">
         <v>9</v>
@@ -1487,67 +1494,67 @@
         <v>33</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C23" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D23" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E23">
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" hidden="1">
       <c r="A24" t="s">
         <v>80</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C24" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D24" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" hidden="1">
       <c r="A25" t="s">
         <v>80</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C25" t="s">
         <v>46</v>
       </c>
       <c r="D25" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E25">
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:5" hidden="1">
       <c r="A26" t="s">
         <v>80</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C26" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D26" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E26">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1555,13 +1562,13 @@
         <v>33</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C27" t="s">
         <v>55</v>
       </c>
       <c r="D27" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E27">
         <v>2</v>
@@ -1572,10 +1579,10 @@
         <v>33</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C28" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D28" t="s">
         <v>64</v>
@@ -1584,8 +1591,31 @@
         <v>8</v>
       </c>
     </row>
+    <row r="29" spans="1:5" hidden="1">
+      <c r="A29" t="s">
+        <v>80</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="C29" t="s">
+        <v>102</v>
+      </c>
+      <c r="D29" t="s">
+        <v>64</v>
+      </c>
+      <c r="E29">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E28" xr:uid="{751A449C-0CEB-BA49-A044-736BF91FB682}"/>
+  <autoFilter ref="A1:E29" xr:uid="{751A449C-0CEB-BA49-A044-736BF91FB682}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="HM002"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E16">
     <sortCondition ref="A1:A16"/>
   </sortState>
@@ -1618,6 +1648,7 @@
     <hyperlink ref="B26" r:id="rId25" xr:uid="{BD0EF741-44F5-B849-8574-53C9AD78F4AD}"/>
     <hyperlink ref="B27" r:id="rId26" xr:uid="{97819A27-9770-AC4D-AB83-857D3AB7B217}"/>
     <hyperlink ref="B28" r:id="rId27" xr:uid="{DDA6D94F-261D-3544-84CA-DD279F702337}"/>
+    <hyperlink ref="B29" r:id="rId28" xr:uid="{75A335A5-E61F-5640-8B15-B4186F3FE177}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/vrcc.xlsx
+++ b/vrcc.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/davidackuaku/Desktop/VRCC/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1A01CAD-1758-8747-A086-C574891F1108}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED1F9A9E-6E58-7440-B1BD-141DEB2E98BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="33600" windowHeight="21000" activeTab="1" xr2:uid="{690D29BB-E107-B54C-8AFA-AAD6A1551766}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" xr2:uid="{690D29BB-E107-B54C-8AFA-AAD6A1551766}"/>
   </bookViews>
   <sheets>
     <sheet name="projects" sheetId="1" r:id="rId1"/>
@@ -1082,10 +1082,10 @@
         <v>103</v>
       </c>
       <c r="D9">
-        <v>6.5918999999999999</v>
+        <v>6.6009000000000002</v>
       </c>
       <c r="E9">
-        <v>0.51739999999999997</v>
+        <v>0.50009999999999999</v>
       </c>
       <c r="F9" s="13" t="s">
         <v>82</v>

--- a/vrcc.xlsx
+++ b/vrcc.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/davidackuaku/Desktop/VRCC/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED1F9A9E-6E58-7440-B1BD-141DEB2E98BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C2DCCFE-769C-1547-8AFF-0F976E65896D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" xr2:uid="{690D29BB-E107-B54C-8AFA-AAD6A1551766}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="33600" windowHeight="21000" xr2:uid="{690D29BB-E107-B54C-8AFA-AAD6A1551766}"/>
   </bookViews>
   <sheets>
     <sheet name="projects" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">media!$A$1:$E$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">media!$A$1:$E$30</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="139">
   <si>
     <t>District</t>
   </si>
@@ -356,6 +356,108 @@
   </si>
   <si>
     <t>First site meeting for the construction Starting for the 24 Hr Economy Market</t>
+  </si>
+  <si>
+    <t>Deme-Fiave Envlave</t>
+  </si>
+  <si>
+    <t>Kharista Road</t>
+  </si>
+  <si>
+    <t>Ho-Deme</t>
+  </si>
+  <si>
+    <t>Ho-Fiave</t>
+  </si>
+  <si>
+    <t>Ho-Adzimakofe</t>
+  </si>
+  <si>
+    <t>Culvert Construction-Some</t>
+  </si>
+  <si>
+    <t>Culvert Construction-Adzimakofe</t>
+  </si>
+  <si>
+    <t>HM006</t>
+  </si>
+  <si>
+    <t>HM007</t>
+  </si>
+  <si>
+    <t>HM008</t>
+  </si>
+  <si>
+    <t>HM009</t>
+  </si>
+  <si>
+    <t>Municipal Assembly</t>
+  </si>
+  <si>
+    <t>Three ongoing culvert construction in the Ho Municipality. Some Culvert.</t>
+  </si>
+  <si>
+    <t>Ho-Some</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dgclahox/image/upload/v1791907259/HM_BRDcs003.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dgclahox/image/upload/v1791907255/HM_BRDcs002.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dgclahox/image/upload/v1791907256/HM_BRDcadz001.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dgclahox/image/upload/v1791907260/HM_BRDcadzi003.jpg</t>
+  </si>
+  <si>
+    <t>Inspection tour conducted at the locations of the Culvert in the Municipal. Ho-Adzimakofe</t>
+  </si>
+  <si>
+    <t>Inspection tour conducted at the locations of the Culvert in the Municipality by Hon Stephen Adom and his team. Ho-Some</t>
+  </si>
+  <si>
+    <t>Inspection tour conducted at the locations of the Culvert in the Municipality by the Hon MCE and his team. Ho-Adzimakofe</t>
+  </si>
+  <si>
+    <t>Inspection tour conducted at the locations of the Culvert in the Municipality by the Hon. MCE and his team. Ho-Adzimakofe</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dgclahox/image/upload/v1791907255/HM_BRDcs001.jpg</t>
+  </si>
+  <si>
+    <t>Work is steadily progressing on the road opening project within the Deme and Fiave enclaves, aimed at improving access and connectivity for residents.</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dgclahox/image/upload/v1791908934/HM_RDfe001.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dgclahox/image/upload/v1791908935/HM_RDfe002.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dgclahox/image/upload/v1791908935/HM_RDfe003.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dgclahox/image/upload/v1791908936/HM_RDfe004.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pictures of work progressing on the Deme Fiave enclaves. </t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dgclahox/image/upload/v1791907258/HM_BRDchtu002.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Steady progress being made on the ongoing road opening works within the Muicipality at Barracks New Town to Kharista School and CK road. This is to improve accessibility, ease trafic flow, and support development within the municipality. Work is expected to be extended to other parts of the municipality. </t>
+  </si>
+  <si>
+    <t>Hon. MCE and his team inspecting work progress.</t>
+  </si>
+  <si>
+    <t>Hon. Ho Municipal Chief Executive and his team inspecting work progress.</t>
+  </si>
+  <si>
+    <t>Hon. Stepehn Adom, the MCE for Ho Municipal and his team inspecting work progress.</t>
   </si>
 </sst>
 </file>
@@ -439,7 +541,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -462,6 +564,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -797,7 +900,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{773B53BD-F917-6C4E-8253-31D0BBDF4EF2}">
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="2" max="2" width="11.83203125" bestFit="1" customWidth="1"/>
@@ -805,7 +908,7 @@
     <col min="6" max="6" width="52.83203125" customWidth="1"/>
     <col min="8" max="8" width="25.83203125" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="21.83203125" customWidth="1"/>
-    <col min="10" max="10" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.6640625" customWidth="1"/>
     <col min="11" max="11" width="18.5" customWidth="1"/>
     <col min="12" max="12" width="30" customWidth="1"/>
   </cols>
@@ -1035,6 +1138,9 @@
       <c r="I7" s="4">
         <v>46258</v>
       </c>
+      <c r="J7" s="14" t="s">
+        <v>116</v>
+      </c>
       <c r="K7" t="s">
         <v>20</v>
       </c>
@@ -1067,6 +1173,9 @@
       <c r="I8" s="4">
         <v>46275</v>
       </c>
+      <c r="J8" s="14" t="s">
+        <v>116</v>
+      </c>
       <c r="K8" t="s">
         <v>67</v>
       </c>
@@ -1096,8 +1205,136 @@
       <c r="H9" s="1" t="s">
         <v>81</v>
       </c>
+      <c r="J9" s="14" t="s">
+        <v>116</v>
+      </c>
       <c r="K9" t="s">
         <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="85">
+      <c r="A10" t="s">
+        <v>112</v>
+      </c>
+      <c r="B10" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="D10">
+        <v>6.6063000000000001</v>
+      </c>
+      <c r="E10">
+        <v>0.47189999999999999</v>
+      </c>
+      <c r="F10" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="G10" t="s">
+        <v>4</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="J10" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="K10" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="51">
+      <c r="A11" t="s">
+        <v>113</v>
+      </c>
+      <c r="B11" t="s">
+        <v>3</v>
+      </c>
+      <c r="C11" t="s">
+        <v>105</v>
+      </c>
+      <c r="D11">
+        <v>6.6037999999999997</v>
+      </c>
+      <c r="E11">
+        <v>0.46879999999999999</v>
+      </c>
+      <c r="F11" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="G11" t="s">
+        <v>4</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="J11" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="K11" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="34">
+      <c r="A12" t="s">
+        <v>114</v>
+      </c>
+      <c r="B12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C12" t="s">
+        <v>110</v>
+      </c>
+      <c r="D12">
+        <v>6.6134000000000004</v>
+      </c>
+      <c r="E12">
+        <v>0.47689999999999999</v>
+      </c>
+      <c r="F12" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="G12" t="s">
+        <v>4</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="J12" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="K12" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
+      <c r="A13" t="s">
+        <v>115</v>
+      </c>
+      <c r="B13" t="s">
+        <v>3</v>
+      </c>
+      <c r="C13" t="s">
+        <v>111</v>
+      </c>
+      <c r="D13">
+        <v>6.6238999999999999</v>
+      </c>
+      <c r="E13">
+        <v>0.47</v>
+      </c>
+      <c r="G13" t="s">
+        <v>4</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="J13" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="K13" t="s">
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -1108,21 +1345,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{751A449C-0CEB-BA49-A044-736BF91FB682}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E43"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="2" max="2" width="89.5" customWidth="1"/>
-    <col min="3" max="3" width="75.33203125" customWidth="1"/>
+    <col min="3" max="3" width="75.33203125" style="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" ht="17">
       <c r="A1" t="s">
         <v>28</v>
       </c>
       <c r="B1" t="s">
         <v>37</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="9" t="s">
         <v>38</v>
       </c>
       <c r="D1" t="s">
@@ -1183,7 +1420,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" hidden="1">
       <c r="A5" t="s">
         <v>33</v>
       </c>
@@ -1200,7 +1437,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" hidden="1">
       <c r="A6" t="s">
         <v>33</v>
       </c>
@@ -1217,7 +1454,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" hidden="1">
       <c r="A7" t="s">
         <v>33</v>
       </c>
@@ -1234,7 +1471,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" hidden="1">
       <c r="A8" t="s">
         <v>33</v>
       </c>
@@ -1251,14 +1488,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:5" hidden="1">
+    <row r="9" spans="1:5" ht="17">
       <c r="A9" t="s">
         <v>58</v>
       </c>
       <c r="B9" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="9" t="s">
         <v>57</v>
       </c>
       <c r="D9" t="s">
@@ -1268,14 +1505,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:5" hidden="1">
+    <row r="10" spans="1:5" ht="17">
       <c r="A10" t="s">
         <v>58</v>
       </c>
       <c r="B10" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="9" t="s">
         <v>57</v>
       </c>
       <c r="D10" t="s">
@@ -1285,14 +1522,14 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:5" hidden="1">
+    <row r="11" spans="1:5" ht="17">
       <c r="A11" t="s">
         <v>58</v>
       </c>
       <c r="B11" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="9" t="s">
         <v>57</v>
       </c>
       <c r="D11" t="s">
@@ -1302,14 +1539,14 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:5" hidden="1">
+    <row r="12" spans="1:5" ht="17">
       <c r="A12" t="s">
         <v>58</v>
       </c>
       <c r="B12" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="9" t="s">
         <v>57</v>
       </c>
       <c r="D12" t="s">
@@ -1438,7 +1675,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" hidden="1">
       <c r="A20" t="s">
         <v>33</v>
       </c>
@@ -1455,7 +1692,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" hidden="1">
       <c r="A21" t="s">
         <v>33</v>
       </c>
@@ -1472,7 +1709,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" hidden="1">
       <c r="A22" t="s">
         <v>33</v>
       </c>
@@ -1489,7 +1726,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:5" hidden="1">
       <c r="A23" t="s">
         <v>33</v>
       </c>
@@ -1557,7 +1794,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:5" hidden="1">
       <c r="A27" t="s">
         <v>33</v>
       </c>
@@ -1574,7 +1811,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:5" hidden="1">
       <c r="A28" t="s">
         <v>33</v>
       </c>
@@ -1608,11 +1845,250 @@
         <v>4</v>
       </c>
     </row>
+    <row r="30" spans="1:5" ht="34">
+      <c r="A30" t="s">
+        <v>114</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="D30" t="s">
+        <v>85</v>
+      </c>
+      <c r="E30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="34">
+      <c r="A31" t="s">
+        <v>114</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="D31" t="s">
+        <v>85</v>
+      </c>
+      <c r="E31">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="34">
+      <c r="A32" t="s">
+        <v>115</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="D32" t="s">
+        <v>85</v>
+      </c>
+      <c r="E32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="17">
+      <c r="A33" t="s">
+        <v>115</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="D33" t="s">
+        <v>85</v>
+      </c>
+      <c r="E33">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="34">
+      <c r="A34" t="s">
+        <v>115</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="C34" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="D34" t="s">
+        <v>85</v>
+      </c>
+      <c r="E34">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="34">
+      <c r="A35" t="s">
+        <v>114</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="C35" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="D35" t="s">
+        <v>85</v>
+      </c>
+      <c r="E35">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="17">
+      <c r="A36" t="s">
+        <v>113</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="C36" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="D36" t="s">
+        <v>85</v>
+      </c>
+      <c r="E36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="17">
+      <c r="A37" t="s">
+        <v>113</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="C37" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="D37" t="s">
+        <v>85</v>
+      </c>
+      <c r="E37">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="17">
+      <c r="A38" t="s">
+        <v>113</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="C38" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="D38" t="s">
+        <v>85</v>
+      </c>
+      <c r="E38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="17">
+      <c r="A39" t="s">
+        <v>113</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="C39" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="D39" t="s">
+        <v>85</v>
+      </c>
+      <c r="E39">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="17">
+      <c r="A40" t="s">
+        <v>112</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="C40" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="D40" t="s">
+        <v>85</v>
+      </c>
+      <c r="E40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="17">
+      <c r="A41" t="s">
+        <v>112</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="C41" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="D41" t="s">
+        <v>85</v>
+      </c>
+      <c r="E41">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" ht="17">
+      <c r="A42" t="s">
+        <v>112</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="C42" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="D42" t="s">
+        <v>85</v>
+      </c>
+      <c r="E42">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" ht="17">
+      <c r="A43" t="s">
+        <v>112</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="C43" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="D43" t="s">
+        <v>85</v>
+      </c>
+      <c r="E43">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E29" xr:uid="{751A449C-0CEB-BA49-A044-736BF91FB682}">
+  <autoFilter ref="A1:E30" xr:uid="{751A449C-0CEB-BA49-A044-736BF91FB682}">
     <filterColumn colId="0">
       <filters>
-        <filter val="HM002"/>
+        <filter val="HM004"/>
+        <filter val="HM008"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -1649,6 +2125,20 @@
     <hyperlink ref="B27" r:id="rId26" xr:uid="{97819A27-9770-AC4D-AB83-857D3AB7B217}"/>
     <hyperlink ref="B28" r:id="rId27" xr:uid="{DDA6D94F-261D-3544-84CA-DD279F702337}"/>
     <hyperlink ref="B29" r:id="rId28" xr:uid="{75A335A5-E61F-5640-8B15-B4186F3FE177}"/>
+    <hyperlink ref="B31" r:id="rId29" xr:uid="{7B3A13F3-ECC7-0B4A-9EC4-77EF525F9A08}"/>
+    <hyperlink ref="B32" r:id="rId30" xr:uid="{380454CB-3E07-664D-BBF3-FE6519AF3A34}"/>
+    <hyperlink ref="B34" r:id="rId31" xr:uid="{D40024C8-F986-3446-81F9-A2C6DC1B004D}"/>
+    <hyperlink ref="B35" r:id="rId32" xr:uid="{6A2747D6-7187-2C49-8AB3-E63FBF1EE131}"/>
+    <hyperlink ref="B30" r:id="rId33" xr:uid="{EE6CF395-1421-B742-8CF9-1A809F458F52}"/>
+    <hyperlink ref="B36" r:id="rId34" xr:uid="{AA92B71D-9F59-4A40-8ADD-41B06697A5E3}"/>
+    <hyperlink ref="B37" r:id="rId35" xr:uid="{F856D732-B5AB-7B40-AF25-A2EF53E4C203}"/>
+    <hyperlink ref="B38" r:id="rId36" xr:uid="{4C1CDA3E-43A9-3240-877B-B89B95A329E8}"/>
+    <hyperlink ref="B39" r:id="rId37" xr:uid="{F425F5E7-F3F2-AF41-B006-F06BECDA154F}"/>
+    <hyperlink ref="B33" r:id="rId38" xr:uid="{1B5B4D62-A43B-6444-9FA3-D58DAEE7FBBE}"/>
+    <hyperlink ref="B40" r:id="rId39" xr:uid="{B8B92E69-40B1-C647-BFF6-D2D2DC453E15}"/>
+    <hyperlink ref="B41" r:id="rId40" xr:uid="{C0B501C6-8E13-2D45-88A6-0564576A563B}"/>
+    <hyperlink ref="B42" r:id="rId41" xr:uid="{FAA66490-C041-2D4F-9945-BF26AA110B79}"/>
+    <hyperlink ref="B43" r:id="rId42" xr:uid="{7EC83354-E347-684E-B4AC-089AA40C073F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/vrcc.xlsx
+++ b/vrcc.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/davidackuaku/Desktop/VRCC/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C2DCCFE-769C-1547-8AFF-0F976E65896D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D18165FD-971E-7A49-B9ED-7FE6520E5857}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="33600" windowHeight="21000" xr2:uid="{690D29BB-E107-B54C-8AFA-AAD6A1551766}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" xr2:uid="{690D29BB-E107-B54C-8AFA-AAD6A1551766}"/>
   </bookViews>
   <sheets>
     <sheet name="projects" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="150">
   <si>
     <t>District</t>
   </si>
@@ -458,6 +458,39 @@
   </si>
   <si>
     <t>Hon. Stepehn Adom, the MCE for Ho Municipal and his team inspecting work progress.</t>
+  </si>
+  <si>
+    <t>Town_Village</t>
+  </si>
+  <si>
+    <t>Agbakofe</t>
+  </si>
+  <si>
+    <t>Denu</t>
+  </si>
+  <si>
+    <t>Ho</t>
+  </si>
+  <si>
+    <t>Kodzobi</t>
+  </si>
+  <si>
+    <t>Titrinu</t>
+  </si>
+  <si>
+    <t>Dave</t>
+  </si>
+  <si>
+    <t>Deme</t>
+  </si>
+  <si>
+    <t>Fiave</t>
+  </si>
+  <si>
+    <t>Some</t>
+  </si>
+  <si>
+    <t>Adzimakofe</t>
   </si>
 </sst>
 </file>
@@ -541,7 +574,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -564,7 +597,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -900,20 +932,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{773B53BD-F917-6C4E-8253-31D0BBDF4EF2}">
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="2" max="2" width="11.83203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="51.5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="52.83203125" customWidth="1"/>
     <col min="8" max="8" width="25.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="21.83203125" customWidth="1"/>
-    <col min="10" max="10" width="18.6640625" customWidth="1"/>
-    <col min="11" max="11" width="18.5" customWidth="1"/>
-    <col min="12" max="12" width="30" customWidth="1"/>
+    <col min="9" max="9" width="25.83203125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="21.83203125" customWidth="1"/>
+    <col min="11" max="11" width="18.6640625" customWidth="1"/>
+    <col min="12" max="12" width="18.5" customWidth="1"/>
+    <col min="13" max="13" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:13">
       <c r="A1" t="s">
         <v>28</v>
       </c>
@@ -938,17 +971,20 @@
       <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="J1" t="s">
         <v>10</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>11</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="76">
+    <row r="2" spans="1:13" ht="76">
       <c r="A2" t="s">
         <v>29</v>
       </c>
@@ -973,18 +1009,21 @@
       <c r="H2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="4">
+      <c r="I2" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="J2" s="4">
         <v>46008</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="K2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>20</v>
       </c>
-      <c r="L2" s="7"/>
-    </row>
-    <row r="3" spans="1:12" ht="18">
+      <c r="M2" s="7"/>
+    </row>
+    <row r="3" spans="1:13" ht="18">
       <c r="A3" t="s">
         <v>30</v>
       </c>
@@ -1009,12 +1048,15 @@
       <c r="H3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K3" t="s">
+      <c r="I3" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="L3" t="s">
         <v>19</v>
       </c>
-      <c r="L3" s="7"/>
-    </row>
-    <row r="4" spans="1:12" ht="95">
+      <c r="M3" s="7"/>
+    </row>
+    <row r="4" spans="1:13" ht="95">
       <c r="A4" t="s">
         <v>31</v>
       </c>
@@ -1039,11 +1081,14 @@
       <c r="H4" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="K4" t="s">
+      <c r="I4" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="L4" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="34">
+    <row r="5" spans="1:13" ht="34">
       <c r="A5" t="s">
         <v>32</v>
       </c>
@@ -1068,14 +1113,17 @@
       <c r="H5" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="I5" s="4">
+      <c r="I5" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="J5" s="4">
         <v>46215</v>
       </c>
-      <c r="K5" t="s">
+      <c r="L5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="34">
+    <row r="6" spans="1:13" ht="34">
       <c r="A6" t="s">
         <v>33</v>
       </c>
@@ -1100,17 +1148,20 @@
       <c r="H6" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="I6" s="10">
+      <c r="I6" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="J6" s="10">
         <v>46148</v>
       </c>
-      <c r="J6" t="s">
+      <c r="K6" t="s">
         <v>40</v>
       </c>
-      <c r="K6" t="s">
+      <c r="L6" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="51">
+    <row r="7" spans="1:13" ht="51">
       <c r="A7" t="s">
         <v>34</v>
       </c>
@@ -1135,17 +1186,20 @@
       <c r="H7" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="I7" s="4">
+      <c r="I7" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="J7" s="4">
         <v>46258</v>
       </c>
-      <c r="J7" s="14" t="s">
+      <c r="K7" t="s">
         <v>116</v>
       </c>
-      <c r="K7" t="s">
+      <c r="L7" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:12" s="11" customFormat="1" ht="51">
+    <row r="8" spans="1:13" s="11" customFormat="1" ht="51">
       <c r="A8" t="s">
         <v>58</v>
       </c>
@@ -1170,17 +1224,20 @@
       <c r="H8" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="I8" s="4">
+      <c r="I8" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="J8" s="4">
         <v>46275</v>
       </c>
-      <c r="J8" s="14" t="s">
+      <c r="K8" t="s">
         <v>116</v>
       </c>
-      <c r="K8" t="s">
+      <c r="L8" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="17">
+    <row r="9" spans="1:13" ht="17">
       <c r="A9" t="s">
         <v>80</v>
       </c>
@@ -1205,14 +1262,17 @@
       <c r="H9" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="J9" s="14" t="s">
+      <c r="I9" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="K9" t="s">
         <v>116</v>
       </c>
-      <c r="K9" t="s">
+      <c r="L9" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="85">
+    <row r="10" spans="1:13" ht="85">
       <c r="A10" t="s">
         <v>112</v>
       </c>
@@ -1237,14 +1297,17 @@
       <c r="H10" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="J10" s="14" t="s">
+      <c r="I10" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="K10" t="s">
         <v>116</v>
       </c>
-      <c r="K10" t="s">
+      <c r="L10" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="51">
+    <row r="11" spans="1:13" ht="51">
       <c r="A11" t="s">
         <v>113</v>
       </c>
@@ -1269,14 +1332,17 @@
       <c r="H11" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="J11" s="14" t="s">
+      <c r="I11" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="K11" t="s">
         <v>116</v>
       </c>
-      <c r="K11" t="s">
+      <c r="L11" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="34">
+    <row r="12" spans="1:13" ht="34">
       <c r="A12" t="s">
         <v>114</v>
       </c>
@@ -1301,14 +1367,17 @@
       <c r="H12" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="J12" s="14" t="s">
+      <c r="I12" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="K12" t="s">
         <v>116</v>
       </c>
-      <c r="K12" t="s">
+      <c r="L12" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="13" spans="1:12">
+    <row r="13" spans="1:13">
       <c r="A13" t="s">
         <v>115</v>
       </c>
@@ -1330,10 +1399,13 @@
       <c r="H13" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="J13" s="14" t="s">
+      <c r="I13" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="K13" t="s">
         <v>116</v>
       </c>
-      <c r="K13" t="s">
+      <c r="L13" t="s">
         <v>67</v>
       </c>
     </row>
